--- a/data/dividends_info_20260321.xlsx
+++ b/data/dividends_info_20260321.xlsx
@@ -5152,7 +5152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C285"/>
+  <dimension ref="A1:C265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5175,7 +5175,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5185,14 +5185,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5202,14 +5202,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5243,7 +5243,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5260,7 +5260,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5270,19 +5270,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5294,29 +5294,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -5328,12 +5328,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -5345,12 +5345,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5362,12 +5362,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5379,12 +5379,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5396,12 +5396,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5413,12 +5413,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5430,46 +5430,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5481,46 +5481,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5532,12 +5532,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5549,12 +5549,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5566,29 +5566,29 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5617,12 +5617,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5634,12 +5634,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5651,29 +5651,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5685,12 +5685,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5702,46 +5702,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5753,29 +5753,29 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5787,12 +5787,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5804,29 +5804,29 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5838,46 +5838,46 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5889,12 +5889,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5906,24 +5906,24 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5940,12 +5940,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5957,12 +5957,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5974,29 +5974,29 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6008,12 +6008,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6025,29 +6025,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6059,12 +6059,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6076,29 +6076,29 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6110,12 +6110,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6127,29 +6127,29 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6161,29 +6161,29 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6195,12 +6195,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6212,46 +6212,46 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6263,24 +6263,24 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6297,7 +6297,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6307,14 +6307,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6331,7 +6331,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6348,7 +6348,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6365,7 +6365,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6382,7 +6382,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6399,12 +6399,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6416,46 +6416,46 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6467,29 +6467,29 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6518,12 +6518,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6535,12 +6535,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6552,12 +6552,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6569,12 +6569,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6586,12 +6586,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6603,29 +6603,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6637,12 +6637,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6654,12 +6654,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6671,12 +6671,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6688,12 +6688,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6705,12 +6705,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6722,24 +6722,24 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6756,7 +6756,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6773,7 +6773,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6790,7 +6790,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6807,7 +6807,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6824,7 +6824,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6875,7 +6875,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6892,7 +6892,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6909,7 +6909,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6919,14 +6919,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6943,7 +6943,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6960,7 +6960,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6977,7 +6977,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6994,12 +6994,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7011,12 +7011,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7028,12 +7028,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7045,12 +7045,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7062,12 +7062,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7079,12 +7079,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7096,12 +7096,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7113,29 +7113,29 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7147,12 +7147,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7164,12 +7164,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7181,12 +7181,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7198,29 +7198,29 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7232,12 +7232,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7249,12 +7249,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7266,29 +7266,29 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7300,12 +7300,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7317,12 +7317,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7334,7 +7334,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -7351,7 +7351,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -7368,7 +7368,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -7385,7 +7385,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -7419,7 +7419,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -7436,7 +7436,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -7453,7 +7453,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -7470,7 +7470,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7504,7 +7504,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -7538,7 +7538,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -7555,7 +7555,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -7572,7 +7572,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -7589,7 +7589,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -7623,7 +7623,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -7640,7 +7640,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -7657,7 +7657,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -7674,7 +7674,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -7691,7 +7691,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -7708,7 +7708,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -7718,14 +7718,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -7742,7 +7742,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -7759,7 +7759,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7776,7 +7776,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7793,7 +7793,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7810,7 +7810,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7827,7 +7827,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -7837,14 +7837,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -7861,7 +7861,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -7878,29 +7878,29 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7912,29 +7912,29 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7946,12 +7946,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7963,12 +7963,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7980,12 +7980,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7997,12 +7997,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -8014,12 +8014,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8031,29 +8031,29 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8065,12 +8065,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8082,29 +8082,29 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8116,12 +8116,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8133,12 +8133,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8150,29 +8150,29 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8184,12 +8184,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8201,12 +8201,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8218,7 +8218,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -8228,14 +8228,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -8252,7 +8252,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -8269,7 +8269,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -8286,7 +8286,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -8296,14 +8296,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -8313,14 +8313,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -8337,46 +8337,46 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8388,29 +8388,29 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8422,63 +8422,63 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8490,80 +8490,80 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Gas Plus S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8575,12 +8575,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8592,97 +8592,97 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -8694,12 +8694,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -8711,46 +8711,46 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -8762,46 +8762,46 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -8813,148 +8813,148 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -8966,12 +8966,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -8983,165 +8983,165 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Autostrade Meridionali S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9153,63 +9153,63 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9221,29 +9221,29 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9255,114 +9255,114 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -9374,80 +9374,80 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -9459,12 +9459,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -9476,12 +9476,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -9493,12 +9493,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Autostrade Meridionali S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -9510,63 +9510,63 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -9578,29 +9578,29 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -9612,29 +9612,29 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -9646,357 +9646,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
           <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C266" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C268" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C269" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B270" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C270" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>INTERCOS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>IGD SIIQ S.p.A.</t>
-        </is>
-      </c>
-      <c r="B272" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>FIDIA S.p.A</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Davide Campari-Milano N.V.</t>
-        </is>
-      </c>
-      <c r="B275" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C275" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>DOTSTAY S.p.A.</t>
-        </is>
-      </c>
-      <c r="B276" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B277" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C277" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="278">
-      <c r="A278" t="inlineStr">
-        <is>
-          <t>Banco BPM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B278" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C278" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="279">
-      <c r="A279" t="inlineStr">
-        <is>
-          <t>BANCA IFIS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B279" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C279" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="280">
-      <c r="A280" t="inlineStr">
-        <is>
-          <t>OVS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr">
-        <is>
-          <t>2026-04-16</t>
-        </is>
-      </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="282">
-      <c r="A282" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr">
-        <is>
-          <t>STAR7 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B283" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="284">
-      <c r="A284" t="inlineStr">
-        <is>
-          <t>Pattern S.p.A.</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" t="inlineStr">
-        <is>
-          <t>RISANAMENTO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B285" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -10047,7 +9707,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10064,7 +9724,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10074,14 +9734,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10098,7 +9758,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10108,7 +9768,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
